--- a/artfynd/A 1324-2025 artfynd.xlsx
+++ b/artfynd/A 1324-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126340349</v>
+        <v>126333727</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Högraningen, Högraningen, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563561</v>
+        <v>563853</v>
       </c>
       <c r="R2" t="n">
-        <v>7306529</v>
+        <v>7306541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,13 +754,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
+          <t>Gammal sumpskog, naturskogsartad</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126335009</v>
+        <v>126333822</v>
       </c>
       <c r="B3" t="n">
-        <v>92180</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,14 +811,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Räftmyran, Räftmyran, Ly lm</t>
+          <t>Högraningen, Högraningen, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563868</v>
+        <v>563772</v>
       </c>
       <c r="R3" t="n">
-        <v>7306298</v>
+        <v>7306545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +853,6 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjolårskropp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -874,7 +865,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gammal sumpskog, naturskogsartad</t>
+          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -892,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126334075</v>
+        <v>126340349</v>
       </c>
       <c r="B4" t="n">
-        <v>79059</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högraningen, Högraningen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563836</v>
+        <v>563561</v>
       </c>
       <c r="R4" t="n">
-        <v>7306467</v>
+        <v>7306529</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +965,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal sumpskog, naturskogsartad</t>
+          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126333727</v>
+        <v>126333835</v>
       </c>
       <c r="B5" t="n">
-        <v>77944</v>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563853</v>
+        <v>563772</v>
       </c>
       <c r="R5" t="n">
-        <v>7306541</v>
+        <v>7306550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126333769</v>
+        <v>126334075</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563850</v>
+        <v>563836</v>
       </c>
       <c r="R6" t="n">
-        <v>7306548</v>
+        <v>7306467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126333822</v>
+        <v>126335670</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1204,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563772</v>
+        <v>563667</v>
       </c>
       <c r="R7" t="n">
-        <v>7306545</v>
+        <v>7306623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1281,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
+          <t>Gammal sumpskog, naturskogsartad</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1304,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126335670</v>
+        <v>126340348</v>
       </c>
       <c r="B8" t="n">
-        <v>91241</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563667</v>
+        <v>563561</v>
       </c>
       <c r="R8" t="n">
-        <v>7306623</v>
+        <v>7306529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal sumpskog, naturskogsartad</t>
+          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1410,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126340348</v>
+        <v>126334049</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,37 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högraningen, Högraningen, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563561</v>
+        <v>563813</v>
       </c>
       <c r="R9" t="n">
-        <v>7306529</v>
+        <v>7306468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,13 +1484,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
+          <t>Gammal sumpskog, naturskogsartad</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1516,45 +1507,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126334049</v>
+        <v>126335009</v>
       </c>
       <c r="B10" t="n">
-        <v>80084</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högraningen, Högraningen, Ly lm</t>
+          <t>Räftmyran, Räftmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563813</v>
+        <v>563868</v>
       </c>
       <c r="R10" t="n">
-        <v>7306468</v>
+        <v>7306298</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,12 +1583,18 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjolårskropp</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1618,32 +1618,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126333835</v>
+        <v>126333769</v>
       </c>
       <c r="B11" t="n">
-        <v>79059</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563772</v>
+        <v>563850</v>
       </c>
       <c r="R11" t="n">
-        <v>7306550</v>
+        <v>7306548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1717,210 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126333694</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högraningen, Högraningen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563888</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7306542</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal sumpskog, naturskogsartad</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126333664</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högraningen, Högraningen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563888</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7306542</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal sumpskog, naturskogsartad</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1324-2025 artfynd.xlsx
+++ b/artfynd/A 1324-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333835</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334075</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335670</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126340348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334049</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126335009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333769</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333694</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,8 +1981,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126333664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>